--- a/refs/heads/main/StructureDefinition-OutbreakToolkitMeaslesDemographic.xlsx
+++ b/refs/heads/main/StructureDefinition-OutbreakToolkitMeaslesDemographic.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T11:26:21+00:00</t>
+    <t>2023-02-08T11:45:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/StructureDefinition-OutbreakToolkitMeaslesDemographic.xlsx
+++ b/refs/heads/main/StructureDefinition-OutbreakToolkitMeaslesDemographic.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-08T11:45:18+00:00</t>
+    <t>2023-02-09T07:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
